--- a/data/trans_orig/IP35_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP35_2023-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3607</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11137</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17749</t>
+          <t>17513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12540</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9744</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>20994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12662</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4539</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22909</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1536,12 +1536,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1571,12 +1571,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8407</t>
+          <t>8574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>18144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9189</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8400</t>
+          <t>8349</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8481</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>18114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20111</t>
+          <t>19990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>32547</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14908</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19448</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2086,12 +2086,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3990</t>
+          <t>3792</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>400</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4289</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>922</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>320</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2655,12 +2655,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13711</t>
+          <t>14083</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27237</t>
+          <t>27990</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15503</t>
+          <t>14956</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30235</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>31492</t>
+          <t>32188</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>52967</t>
+          <t>52328</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9736</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>21075</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11122</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>25658</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23488</t>
+          <t>23566</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41395</t>
+          <t>41837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -2881,12 +2881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3087</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9795</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8030</t>
+          <t>8096</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>507</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>501</t>
+          <t>489</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18560</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32545</t>
+          <t>33436</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23136</t>
+          <t>23585</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31722</t>
+          <t>31877</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50752</t>
+          <t>50934</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34042</t>
+          <t>34407</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13665</t>
+          <t>13297</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>33813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54805</t>
+          <t>56061</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -3333,12 +3333,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12167</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3348,12 +3348,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>15122</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>29318</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17225</t>
+          <t>17026</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33554</t>
+          <t>33910</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>26020</t>
+          <t>24910</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43415</t>
+          <t>43340</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>46958</t>
+          <t>45283</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>70869</t>
+          <t>70090</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -3559,12 +3559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30775</t>
+          <t>31768</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>24787</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>44557</t>
+          <t>43481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46318</t>
+          <t>45138</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>68305</t>
+          <t>69834</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7319</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>26604</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21494</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -3785,47 +3785,47 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>3253</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>358</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>2915</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>1565</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>587</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>5732</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>796</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>16173</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>32107</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>46621</t>
+          <t>45920</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>43380</t>
+          <t>43377</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>72729</t>
+          <t>71871</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>8852</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20780</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>30178</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>24587</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>45731</t>
+          <t>45362</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,74%</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2589</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13901</t>
+          <t>14874</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>492</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4549</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -4806,12 +4806,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>16185</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>31733</t>
+          <t>30533</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4821,12 +4821,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>18101</t>
+          <t>17558</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>36261</t>
+          <t>34613</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38271</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>63964</t>
+          <t>62535</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -4919,12 +4919,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15698</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>33858</t>
+          <t>33809</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7808</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>21609</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>49734</t>
+          <t>49893</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -5032,12 +5032,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5047,12 +5047,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>14621</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>31437</t>
+          <t>31131</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>43097</t>
+          <t>43628</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>17225</t>
+          <t>17398</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>32591</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>20245</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>39063</t>
+          <t>37792</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5195,12 +5195,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>42534</t>
+          <t>41493</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>66125</t>
+          <t>64766</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -5258,12 +5258,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>23360</t>
+          <t>24432</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>41727</t>
+          <t>42402</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5273,12 +5273,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>34143</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>58384</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63924</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>92674</t>
+          <t>93370</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5371,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>27482</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5386,12 +5386,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7427</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>20593</t>
+          <t>22148</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5421,12 +5421,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>41286</t>
+          <t>41030</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5456,12 +5456,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -5484,12 +5484,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>8258</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5499,12 +5499,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>557</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7461</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4642</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -5945,7 +5945,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>633</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>6898</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>20184</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>41899</t>
+          <t>41573</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>32043</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>54248</t>
+          <t>55721</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>56901</t>
+          <t>56133</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>89294</t>
+          <t>88401</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -6166,12 +6166,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>26654</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>20988</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>20759</t>
+          <t>21778</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>41560</t>
+          <t>41825</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>8370</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10245</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>514</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>483</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -6505,12 +6505,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>25665</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>50859</t>
+          <t>50543</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6520,12 +6520,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>26127</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>50713</t>
+          <t>50541</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6555,12 +6555,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>56338</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>92329</t>
+          <t>92662</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -6618,12 +6618,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>17188</t>
+          <t>18726</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>37684</t>
+          <t>38757</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6633,12 +6633,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>21166</t>
+          <t>20905</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>47136</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>46244</t>
+          <t>45781</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>77156</t>
+          <t>79010</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6731,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>10425</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>26871</t>
+          <t>26902</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6746,12 +6746,12 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>35823</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6781,12 +6781,12 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>29230</t>
+          <t>30862</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>54460</t>
+          <t>55496</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -6844,12 +6844,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>35031</t>
+          <t>33764</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>129917</t>
+          <t>124510</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>26423</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>76096</t>
+          <t>74464</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>67709</t>
+          <t>69712</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>194228</t>
+          <t>187553</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -6957,12 +6957,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>39185</t>
+          <t>38708</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>67580</t>
+          <t>68781</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>62189</t>
+          <t>62091</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>100582</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7007,12 +7007,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>111245</t>
+          <t>112458</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>157464</t>
+          <t>159239</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -7070,12 +7070,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>11846</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>40753</t>
+          <t>40976</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>16551</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>36050</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>32443</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>65279</t>
+          <t>67233</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -7183,12 +7183,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>13131</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3685</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>16794</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7531,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2477</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -7639,12 +7639,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -7752,12 +7752,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>64303</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>95848</t>
+          <t>94175</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>85977</t>
+          <t>84300</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>126235</t>
+          <t>123240</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>157042</t>
+          <t>158994</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>206400</t>
+          <t>207034</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -7865,12 +7865,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>41326</t>
+          <t>40614</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>66081</t>
+          <t>65489</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>46768</t>
+          <t>46001</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>74403</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>94889</t>
+          <t>95445</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>131304</t>
+          <t>130783</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -7978,12 +7978,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9083</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>18633</t>
+          <t>19529</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>36972</t>
+          <t>36168</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -8096,7 +8096,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10019</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>77009</t>
+          <t>75975</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>111011</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>70363</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>104241</t>
+          <t>104907</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>154625</t>
+          <t>155580</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>203407</t>
+          <t>202584</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8317,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>63604</t>
+          <t>64875</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>96272</t>
+          <t>96169</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>60125</t>
+          <t>59276</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>92968</t>
+          <t>90632</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8367,12 +8367,12 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>131214</t>
+          <t>132047</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>177486</t>
+          <t>178201</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -8430,12 +8430,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>29735</t>
+          <t>31773</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>51794</t>
+          <t>52611</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>53631</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>84434</t>
+          <t>83478</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8480,12 +8480,12 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8500,12 +8500,12 @@
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>91750</t>
+          <t>90496</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>127591</t>
+          <t>128065</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -8543,12 +8543,12 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>92745</t>
+          <t>93404</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>195311</t>
+          <t>194431</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8558,12 +8558,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8578,12 +8578,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>93957</t>
+          <t>94479</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>151219</t>
+          <t>150271</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>199766</t>
+          <t>201855</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>323799</t>
+          <t>308942</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -8656,12 +8656,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>99893</t>
+          <t>99613</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>138091</t>
+          <t>138386</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8691,12 +8691,12 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>138180</t>
+          <t>139247</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>183911</t>
+          <t>189863</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8706,12 +8706,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>251117</t>
+          <t>251966</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>313341</t>
+          <t>311459</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>36365</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>72500</t>
+          <t>73144</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>46947</t>
+          <t>45709</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>73989</t>
+          <t>75013</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>88996</t>
+          <t>88388</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>133332</t>
+          <t>136719</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -8882,12 +8882,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>17380</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8917,12 +8917,12 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5830</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>14174</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>32278</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -8995,12 +8995,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>483</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>5544</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9030,12 +9030,12 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9045,12 +9045,12 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>10499</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9085,7 +9085,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
